--- a/EDA/FIS_Analysis_Final.xlsx
+++ b/EDA/FIS_Analysis_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fc4bd521ffc22738/Desktop/Freelancing/AIGEN/smartsentry_aml_model/EDA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D229CADD35EB4FDC579760892F570FD2FE4A6E5A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{513ECC16-F86D-469D-8767-2A06B5AC0359}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_D229CADD35EB4FDC579760892F570FD2FE4A6E5A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37B84522-009A-4554-8DC5-A85182C538F3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIS Results &amp; Validation" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,24 @@
     <sheet name="Customer Risk Detail" sheetId="3" r:id="rId3"/>
     <sheet name="Formula Reference" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="122">
   <si>
     <t>FRAUD INTENSITY SCORE — Results &amp; Validation  |  max_rule=27  |  KYC: low=1, medium=2, high=3</t>
   </si>
@@ -451,6 +462,9 @@
   </si>
   <si>
     <t>100.0 → critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -605,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -676,20 +690,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -703,6 +708,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,36 +1032,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1284,20 +1292,20 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1332,73 +1340,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
     </row>
     <row r="2" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
     </row>
     <row r="3" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
     </row>
     <row r="4" spans="1:19" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1755,27 +1763,27 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1790,7 +1798,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1804,43 +1812,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
     </row>
     <row r="2" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2017,17 +2025,27 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2046,238 +2064,238 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="2" max="2" width="14" style="31" customWidth="1"/>
+    <col min="3" max="3" width="44" style="31" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="31" customWidth="1"/>
+    <col min="5" max="5" width="28" style="31" customWidth="1"/>
+    <col min="6" max="6" width="36" style="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="3" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+    </row>
+    <row r="3" spans="1:6" s="31" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="23" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="25" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="24" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="25" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="24" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="25" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="24" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="25" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="24" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="25" t="s">
         <v>120</v>
       </c>
     </row>
